--- a/hedexamples/data/spreadsheet_data/ExcelMultipleSheets.xlsx
+++ b/hedexamples/data/spreadsheet_data/ExcelMultipleSheets.xlsx
@@ -5,164 +5,73 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\HEDPython\hed-python\hedvalidation\tests\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\HEDPython\hed-python\webtools\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23680" windowHeight="11050" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8194" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="LKT Events" sheetId="1" r:id="rId1"/>
-    <sheet name="PVT Events" sheetId="2" r:id="rId2"/>
-    <sheet name="DAS Events" sheetId="3" r:id="rId3"/>
+    <sheet name="LKT 8HED3" sheetId="4" r:id="rId1"/>
+    <sheet name="LKT Events" sheetId="1" r:id="rId2"/>
+    <sheet name="PVT Events" sheetId="2" r:id="rId3"/>
+    <sheet name="DAS Events" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
   <si>
     <t>Event code</t>
   </si>
   <si>
+    <t>Short label</t>
+  </si>
+  <si>
     <t>Description in text</t>
   </si>
   <si>
-    <t>Event category</t>
-  </si>
-  <si>
     <t>HED tags</t>
   </si>
   <si>
-    <t>Short label</t>
-  </si>
-  <si>
     <t>PerturbLeft</t>
   </si>
   <si>
+    <t>Vehicle undergoes a perturbation to left.</t>
+  </si>
+  <si>
+    <t>Event/Category/Participant response, (Item/Object/Vehicle/Car, Attribute/Object control/Perturb), Attribute/Direction/Right, Attribute/Onset</t>
+  </si>
+  <si>
     <t>PerturbRight</t>
   </si>
   <si>
+    <t>Vehicle undergoes a perturbation to right.</t>
+  </si>
+  <si>
     <t>ResponseOnset</t>
   </si>
   <si>
+    <t>Subject starts to respond to perturbation by steering vehicle back to center of the lane.</t>
+  </si>
+  <si>
     <t>ResponseOffset</t>
   </si>
   <si>
+    <t>Subject completes response to perturbation having steered the vehicle back to the center of the lane.</t>
+  </si>
+  <si>
+    <t>Sector start</t>
+  </si>
+  <si>
     <t>The start of increasing the size of the sector</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Short label</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sector start</t>
-  </si>
-  <si>
-    <t>Correct BUT down</t>
-  </si>
-  <si>
-    <t>Incorrect BUT down</t>
-  </si>
-  <si>
-    <t>Auditory buzz indicating participant did not respond to the stimulus after stimulus appeared</t>
-  </si>
-  <si>
-    <t>Buzz no response</t>
-  </si>
-  <si>
-    <t>Start PVT</t>
-  </si>
-  <si>
-    <t>The start of Psychomotor Vigilance Task</t>
-  </si>
-  <si>
-    <t>Event/Category/Participant response, (Participant ~ Action/Control Vehicle/Drive/Correct ~ Item/Object/Vehicle/Car), Attribute/Onset</t>
-  </si>
-  <si>
-    <t>Event/Category/Participant response, (Item/Object/Vehicle/Car, Attribute/Object control/Perturb), Attribute/Direction/Right, Attribute/Onset</t>
-  </si>
-  <si>
-    <t>Event/Category/Participant response, (Participant ~ Action/Control Vehicle/Drive/Correct ~ Item/Object/Vehicle/Car), Attribute/Offset</t>
-  </si>
-  <si>
-    <t>Vehicle undergoes a perturbation to left.</t>
-  </si>
-  <si>
-    <t>Vehicle undergoes a perturbation to right.</t>
-  </si>
-  <si>
-    <t>Subject starts to respond to perturbation by steering vehicle back to center of the lane.</t>
-  </si>
-  <si>
-    <t>Subject completes response to perturbation having steered the vehicle back to the center of the lane.</t>
-  </si>
-  <si>
-    <t>DAS start</t>
-  </si>
-  <si>
-    <t>The start of lane-keeping driving with DAS task or the start of pure DAS session.</t>
-  </si>
-  <si>
-    <t>Event/Description/The start of lane-keeping driving with DAS task or the start of pure DAS session.,
-Event/Label/DAS start, Attribute/Onset, Event/Category/Experiment control/Experiment</t>
-  </si>
-  <si>
-    <t>Event/Description/An attention cue in the form of a red written word saying Attention! appeared on the left to request attending to the left visual stimuli for animal target names., Event/Label/Left visual cue, 
-Event/Category/Experimental stimulus/Instruction/Attend,
-(Item/Symbolic/Character/Letter, Sensory presentation/Visual/Rendering type/Screen/2D, Attribute/Location/Screen/Left, Attribute/Language/Unit/Word/Verb/Attention,
-Attribute/Color/Red, Participant/Effect/Visual, Participant/Effect/Cognitive/Meaningful,
-Attribute/Onset)</t>
-  </si>
-  <si>
-    <t>Left visual cue</t>
-  </si>
-  <si>
-    <t>Right visual cue</t>
-  </si>
-  <si>
-    <t>Left auditory cue</t>
-  </si>
-  <si>
-    <t>Right auditory cue</t>
-  </si>
-  <si>
-    <t>An attention cue in the form of a red written word saying Attention! appeared on the left to request attending to the left visual stimuli for animal target names.</t>
-  </si>
-  <si>
-    <t>An attention cue in the form of a red written word saying Attention! appeared on the right to request attending to the right visual stimuli for animal target names.</t>
-  </si>
-  <si>
-    <t>An attention cue in the form of sound coming from the left speaker saying Attention was played to request attending to the left auditory stimuli for animal target names.</t>
-  </si>
-  <si>
-    <t>An attention cue in the form of sound coming from the right speaker saying Attention was played to request attending to the right auditory stimuli for animal target names.</t>
-  </si>
-  <si>
-    <t>Event/Description/An attention cue in the form of sound coming from the left speaker saying Attention was played to request attending to the left auditory stimuli for animal target names., Event/Label/Left auditory cue,
-Event/Category/Experimental stimulus/Instruction/Attend, 
- (Item, Sensory presentation/Auditory/Human Voice, Attribute/Location/Reference frame/Relative to Participant/Left, Attribute/Language/Unit/Word/Verb/Attention, 
-Participant/Effect/Auditory, Participant/Effect/Cognitive/Meaningful, Attribute/Onset)</t>
-  </si>
-  <si>
-    <t>Event/Description/An attention cue in the form of sound coming from the right speaker saying Attention was played to request attending to the right auditory stimuli for animal target names., Event/Label/Right auditory cue,
-Event/Category/Experimental stimulus/Instruction/Attend, 
- (Item, Sensory presentation/Auditory/Human Voice, Attribute/Location/Reference frame/Relative to Participant/Right, Attribute/Language/Unit/Word/Verb/Attention, 
-Participant/Effect/Auditory, Participant/Effect/Cognitive/Meaningful, Attribute/Onset)</t>
-  </si>
-  <si>
-    <t>Event/Description/An attention cue in the form of a red written word saying Attention! appeared on the right to request attending to the right visual stimuli for animal target names., Event/Label/Right visual cue, 
-Event/Category/Experimental stimulus/Instruction/Attend, 
-(Item/Symbolic/Character/Letter, Sensory presentation/Visual/Rendering type/Screen/2D, Attribute/Location/Screen/Right, Attribute/Language/Unit/Word/Verb/Attention,
-Attribute/Color/Red, Participant/Effect/Visual, Participant/Effect/Cognitive/Meaningful, 
-Attribute/Onset)</t>
   </si>
   <si>
     <t>Event/Category/Experimental stimulus/Instruction/Attend,
@@ -173,42 +82,47 @@
 Participant/Effect/Cognitive/Target</t>
   </si>
   <si>
-    <t>Event/Category/Experimental stimulus/Instruction/Attend,
-Participant/State/Attention/Alerting, 
-Sensory presentation/Auditory/Buzz, Experiment control /Activity/Participant action/Time out</t>
+    <t>Correct BUT down</t>
+  </si>
+  <si>
+    <t>Correct to respond to the stimulus Button Down</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t>Event/Category/Participant response,</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color indexed="10"/>
+        <color rgb="FFFF0000"/>
         <rFont val="新細明體"/>
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> 
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">
-(Participant, Action/Button hold/Keyboard), Attribute/Action judgment/Correct
+      <t>(Participant, Action/Button hold/Keyboard), Attribute/Action judgment/Correct
 Experiment control/Activity/Participant action, Action/Button press/Keyboard</t>
     </r>
   </si>
   <si>
-    <t>Event/Category/Experiment control/Sequence/Experiment, Attribute/Onset</t>
-  </si>
-  <si>
-    <t>Correct to respond to the stimulus Button Down</t>
+    <t>Incorrect BUT down</t>
   </si>
   <si>
     <t>Incorrect to respond to the stimulus Button Down</t>
@@ -217,44 +131,159 @@
     <t>Event/Category/Participant response,
 (Participant, Action/Button hold/Keyboard),  Action/Button press/Keyboard,
 Experiment control/Activity/Participant action/Incorrect</t>
+  </si>
+  <si>
+    <t>Buzz no response</t>
+  </si>
+  <si>
+    <t>Auditory buzz indicating participant did not respond to the stimulus after stimulus appeared</t>
+  </si>
+  <si>
+    <t>Event/Category/Experimental stimulus/Instruction/Attend,
+Participant/State/Attention/Alerting, 
+Sensory presentation/Auditory/Buzz, Experiment control /Activity/Participant action/Time out</t>
+  </si>
+  <si>
+    <t>Start PVT</t>
+  </si>
+  <si>
+    <t>The start of Psychomotor Vigilance Task</t>
+  </si>
+  <si>
+    <t>Event/Category/Experiment control/Sequence/Experiment, Attribute/Onset</t>
+  </si>
+  <si>
+    <t>Event category</t>
+  </si>
+  <si>
+    <t>DAS start</t>
+  </si>
+  <si>
+    <t>The start of lane-keeping driving with DAS task or the start of pure DAS session.</t>
+  </si>
+  <si>
+    <t>Event/Description/The start of lane-keeping driving with DAS task or the start of pure DAS session.,
+Event/Label/DAS start, Attribute/Onset, Event/Category/Experiment control/Experiment</t>
+  </si>
+  <si>
+    <t>Left visual cue</t>
+  </si>
+  <si>
+    <t>An attention cue in the form of a red written word saying Attention! appeared on the left to request attending to the left visual stimuli for animal target names.</t>
+  </si>
+  <si>
+    <t>Event/Description/An attention cue in the form of a red written word saying Attention! appeared on the left to request attending to the left visual stimuli for animal target names., Event/Label/Left visual cue, 
+Event/Category/Experimental stimulus/Instruction/Attend,
+(Item/Symbolic/Character/Letter, Sensory presentation/Visual/Rendering type/Screen/2D, Attribute/Location/Screen/Left, Attribute/Language/Unit/Word/Verb/Attention,
+Attribute/Color/Red, Participant/Effect/Visual, Participant/Effect/Cognitive/Meaningful,
+Attribute/Onset)</t>
+  </si>
+  <si>
+    <t>Right visual cue</t>
+  </si>
+  <si>
+    <t>An attention cue in the form of a red written word saying Attention! appeared on the right to request attending to the right visual stimuli for animal target names.</t>
+  </si>
+  <si>
+    <t>Event/Description/An attention cue in the form of a red written word saying Attention! appeared on the right to request attending to the right visual stimuli for animal target names., Event/Label/Right visual cue, 
+Event/Category/Experimental stimulus/Instruction/Attend, 
+(Item/Symbolic/Character/Letter, Sensory presentation/Visual/Rendering type/Screen/2D, Attribute/Location/Screen/Right, Attribute/Language/Unit/Word/Verb/Attention,
+Attribute/Color/Red, Participant/Effect/Visual, Participant/Effect/Cognitive/Meaningful, 
+Attribute/Onset)</t>
+  </si>
+  <si>
+    <t>Left auditory cue</t>
+  </si>
+  <si>
+    <t>An attention cue in the form of sound coming from the left speaker saying Attention was played to request attending to the left auditory stimuli for animal target names.</t>
+  </si>
+  <si>
+    <t>Event/Description/An attention cue in the form of sound coming from the left speaker saying Attention was played to request attending to the left auditory stimuli for animal target names., Event/Label/Left auditory cue,
+Event/Category/Experimental stimulus/Instruction/Attend, 
+ (Item, Sensory presentation/Auditory/Human Voice, Attribute/Location/Reference frame/Relative to Participant/Left, Attribute/Language/Unit/Word/Verb/Attention, 
+Participant/Effect/Auditory, Participant/Effect/Cognitive/Meaningful, Attribute/Onset)</t>
+  </si>
+  <si>
+    <t>Right auditory cue</t>
+  </si>
+  <si>
+    <t>An attention cue in the form of sound coming from the right speaker saying Attention was played to request attending to the right auditory stimuli for animal target names.</t>
+  </si>
+  <si>
+    <t>Event/Description/An attention cue in the form of sound coming from the right speaker saying Attention was played to request attending to the right auditory stimuli for animal target names., Event/Label/Right auditory cue,
+Event/Category/Experimental stimulus/Instruction/Attend, 
+ (Item, Sensory presentation/Auditory/Human Voice, Attribute/Location/Reference frame/Relative to Participant/Right, Attribute/Language/Unit/Word/Verb/Attention, 
+Participant/Effect/Auditory, Participant/Effect/Cognitive/Meaningful, Attribute/Onset)</t>
+  </si>
+  <si>
+    <t>Test Pound Sign</t>
+  </si>
+  <si>
+    <t>Test Event for Pound Sign Detection</t>
+  </si>
+  <si>
+    <t>Event/Category/Technical error/This is a technical error string</t>
+  </si>
+  <si>
+    <t>Event/Category/Participant response, (Participant, (Action/Control Vehicle/Drive/Correct, Item/Object/Vehicle/Car)), Attribute/Onset</t>
+  </si>
+  <si>
+    <t>Event/Category/Participant response, (Participant,  (Action/Control Vehicle/Drive/Correct,  Item/Object/Vehicle/Car)), Attribute/Offset</t>
+  </si>
+  <si>
+    <t>Long name</t>
+  </si>
+  <si>
+    <t>PerturbCarToLeft</t>
+  </si>
+  <si>
+    <t>PerturbCarToRight</t>
+  </si>
+  <si>
+    <t>DriverStopsCorrecting</t>
+  </si>
+  <si>
+    <t>DriverStartsToCorrect</t>
+  </si>
+  <si>
+    <t>Experiment-control, Experimental-stimulus, (Controller-agent, (Operate, Car, (Turn, Leftward)))</t>
+  </si>
+  <si>
+    <t>Experiment-control, Experimental-stimulus, (Controller-agent, (Operate, Car, (Turn, Rightward)))</t>
+  </si>
+  <si>
+    <t>Agent-action, Participant-response, (Halt, Correction)</t>
+  </si>
+  <si>
+    <t>Subject completes response to perturbation having steered the vehicle back to the center of the lane. Normally this would be tagged with temporal scope, but avoiding definitions here.</t>
+  </si>
+  <si>
+    <t>Agent-action, Participant-response, Correction, ((Human-agent, Experiment-participant), (Modify, (Car,Angle)))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="10"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
@@ -278,40 +307,40 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom/>
@@ -321,51 +350,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -648,204 +674,323 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" style="14" customWidth="1"/>
-    <col min="2" max="2" width="23.08984375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="57.36328125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="41.90625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="23.07421875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="57.3828125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="41.921875" style="2" customWidth="1"/>
+    <col min="6" max="1026" width="8.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="43.75">
+      <c r="A2" s="1">
+        <v>251</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="43.75">
+      <c r="A3" s="1">
+        <v>252</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="47.05" customHeight="1">
+      <c r="A4" s="1">
+        <v>253</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="58">
-      <c r="A2" s="14">
-        <v>251</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="58">
-      <c r="A3" s="14">
-        <v>252</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="47" customHeight="1">
-      <c r="A4" s="14">
-        <v>253</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="58">
-      <c r="A5" s="14">
+      <c r="E4" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.75">
+      <c r="A5" s="1">
         <v>254</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>20</v>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="26.36328125" customWidth="1"/>
-    <col min="2" max="2" width="25.6328125" customWidth="1"/>
-    <col min="3" max="3" width="54" customWidth="1"/>
-    <col min="4" max="4" width="73.36328125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="23.07421875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="57.3828125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="41.921875" style="2" customWidth="1"/>
+    <col min="6" max="1026" width="8.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="58.3">
+      <c r="A2" s="1">
+        <v>251</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="87">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="58.3">
+      <c r="A3" s="1">
+        <v>252</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="47.05" customHeight="1">
+      <c r="A4" s="1">
+        <v>253</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="58.3">
+      <c r="A5" s="1">
+        <v>254</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="44">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="43.5">
-      <c r="A4" s="5">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="58">
-      <c r="A5" s="5">
-        <v>32</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="5">
-        <v>64</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>43</v>
+      <c r="E5" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="69.54296875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="118.08984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="55.08984375" customWidth="1"/>
+    <col min="1" max="1" width="26.3828125" customWidth="1"/>
+    <col min="2" max="2" width="25.61328125" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
+    <col min="4" max="4" width="73.3828125" style="5" customWidth="1"/>
+    <col min="5" max="1025" width="8.53515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="87.45">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="44.6">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.75">
+      <c r="A4" s="8">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="58.3">
+      <c r="A5" s="8">
+        <v>32</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="8">
+        <v>64</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.6"/>
+  <cols>
+    <col min="1" max="1" width="17.61328125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="24.84375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="69.53515625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="118.07421875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="55.07421875" customWidth="1"/>
+    <col min="6" max="1025" width="8.53515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -853,90 +998,104 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29">
-      <c r="A2" s="5">
+    <row r="2" spans="1:5" ht="29.15">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="101.5">
-      <c r="A3" s="5">
+      <c r="B2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="102">
+      <c r="A3" s="8">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="101.5">
-      <c r="A4" s="5">
+      <c r="D3" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="102">
+      <c r="A4" s="8">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="B4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="87.45">
+      <c r="A5" s="8">
+        <v>13</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="87">
-      <c r="A5" s="5">
-        <v>13</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="87">
-      <c r="A6" s="5">
+      <c r="D5" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="87.45">
+      <c r="A6" s="8">
         <v>14</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>38</v>
+      <c r="B6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="8">
+        <v>55</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>